--- a/word-monitor-sub-domain/report/history/keyword-table-20260711-004842.xlsx
+++ b/word-monitor-sub-domain/report/history/keyword-table-20260711-004842.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>338</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
